--- a/Results/Phase 2/Methanol/methanol eutrophication freshwater results.xlsx
+++ b/Results/Phase 2/Methanol/methanol eutrophication freshwater results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.282483106560997e-05</v>
+        <v>2.478615621372116e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.260010856295497e-05</v>
+        <v>1.237119440171238e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.370580437585137e-05</v>
+        <v>1.304129314032404e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.749277306707635e-05</v>
+        <v>1.519856073396994e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.40212465975766e-05</v>
+        <v>1.321398090975426e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.514995180123309e-05</v>
+        <v>1.395029453370815e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.438715275070763e-05</v>
+        <v>1.341534718942047e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.401514820037075e-05</v>
+        <v>1.321625093795409e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.823558979250501e-05</v>
+        <v>1.577941467429973e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.352422965966803e-05</v>
+        <v>1.293824847523007e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>4.360338480975171e-05</v>
+        <v>3.085947403292145e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>2.386593997226719e-05</v>
+        <v>1.892134986746429e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.276873577433189e-05</v>
+        <v>1.249976396365471e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.833436538484163e-05</v>
+        <v>1.725518938985116e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.944313853875301e-05</v>
+        <v>1.656829684248378e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.597805593883783e-05</v>
+        <v>1.438281464953336e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.371087757598988e-05</v>
+        <v>1.303518477606559e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>2.116843674110392e-05</v>
+        <v>1.75866385841882e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.501452085537818e-05</v>
+        <v>1.380035352292781e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>3.386646577074367e-05</v>
+        <v>2.621761120582194e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.673088877485598e-05</v>
+        <v>1.492522630644054e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.884554478212525e-05</v>
+        <v>1.722884684369113e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>2.25349683821325e-05</v>
+        <v>1.821309541515924e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.557844716674515e-05</v>
+        <v>1.416833175449127e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.425047826535982e-05</v>
+        <v>2.054406249350124e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.961428555602789e-05</v>
+        <v>1.655268513807584e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.692161429081931e-05</v>
+        <v>2.058408730749107e-05</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.104544596368872e-05</v>
+        <v>1.097850923742566e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.112047502896847e-05</v>
+        <v>1.105239927392881e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.122403233946112e-05</v>
+        <v>1.108027395744241e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.088733782862087e-05</v>
+        <v>1.082129313160452e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.130038594576029e-05</v>
+        <v>1.11255465275844e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.163360348143202e-05</v>
+        <v>1.134119210364105e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.104509681233325e-05</v>
+        <v>1.097460262945062e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.13098706588219e-05</v>
+        <v>1.113094509960594e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.156944233707093e-05</v>
+        <v>1.129536157822171e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.265626682357592e-05</v>
+        <v>1.19610255336655e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>1.206326201344095e-05</v>
+        <v>1.1601718584585e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>1.162574127933293e-05</v>
+        <v>1.131669912370773e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.107410826614761e-05</v>
+        <v>1.099624535109721e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.282736830863151e-05</v>
+        <v>1.272578987777495e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.115975131405306e-05</v>
+        <v>1.104864592800928e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.125318968615936e-05</v>
+        <v>1.110159581002176e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.110038014303186e-05</v>
+        <v>1.100854050730901e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.208589579349377e-05</v>
+        <v>1.162190521205208e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.114480781656354e-05</v>
+        <v>1.103547611525157e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>1.486695845767745e-05</v>
+        <v>1.404478451168066e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.139227789809525e-05</v>
+        <v>1.11900339774965e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33870805757351e-05</v>
+        <v>1.319442963353857e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.694387929082782e-05</v>
+        <v>1.45175436792032e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.474725886877277e-05</v>
+        <v>1.316614423829619e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.193632833799694e-05</v>
+        <v>1.183057301054437e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.165104363427193e-05</v>
+        <v>1.133828480925347e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.169104180199544e-05</v>
+        <v>1.134816923903091e-05</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.936091185450487e-05</v>
+        <v>2.261010701368454e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.213572979783279e-05</v>
+        <v>1.201474140893538e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.520659853210392e-05</v>
+        <v>1.382656831671917e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.639882979220049e-05</v>
+        <v>1.448277842938108e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.381123876269824e-05</v>
+        <v>1.301122748531471e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.489260167680849e-05</v>
+        <v>1.371646641928361e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.238763520910637e-05</v>
+        <v>1.21803062054218e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.316264516152643e-05</v>
+        <v>1.263355414090815e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.753978841781175e-05</v>
+        <v>1.527617071401436e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.354109746536681e-05</v>
+        <v>1.287615487045839e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>4.387233277533089e-05</v>
+        <v>3.093412413162816e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>2.300328059464554e-05</v>
+        <v>1.834604612180749e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.304557042019265e-05</v>
+        <v>1.257614425266661e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.789377966389014e-05</v>
+        <v>1.683442083529019e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>2.121174999476008e-05</v>
+        <v>1.756614622072514e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.555957815842131e-05</v>
+        <v>1.4054182904256e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.245028492992788e-05</v>
+        <v>1.221929096323661e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>2.120691927895032e-05</v>
+        <v>1.754674852867894e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.564771049528794e-05</v>
+        <v>1.408398266331028e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>3.296033086387636e-05</v>
+        <v>2.550033299987851e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.464981305787818e-05</v>
+        <v>1.359202139467728e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.722457264435265e-05</v>
+        <v>1.60674083157547e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>2.326832722110093e-05</v>
+        <v>1.856765701707372e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.489172938151945e-05</v>
+        <v>1.368116275983733e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.194703727482543e-05</v>
+        <v>1.89076643184393e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.758321370317643e-05</v>
+        <v>1.527478677042909e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.63030886353931e-05</v>
+        <v>2.013728888678593e-05</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.64072601358386e-05</v>
+        <v>2.079311995314861e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.226496424072604e-05</v>
+        <v>1.213757724061119e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.653872956460417e-05</v>
+        <v>1.46666458374279e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.547560133894551e-05</v>
+        <v>1.395254605841556e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.498432699333035e-05</v>
+        <v>1.375859286639678e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.502728044124657e-05</v>
+        <v>1.385954542256442e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.221563656664728e-05</v>
+        <v>1.213945922169308e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.71785644144733e-05</v>
+        <v>1.502069585911991e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.792757187514208e-05</v>
+        <v>1.557247693636165e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.979888092900274e-05</v>
+        <v>1.676602660963485e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>4.068711742481049e-05</v>
+        <v>2.912605523546443e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>2.223569028432123e-05</v>
+        <v>1.795244069472053e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.362306271354037e-05</v>
+        <v>1.297071028392491e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.794723866999864e-05</v>
+        <v>1.694785728214554e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>2.139955973894586e-05</v>
+        <v>1.775835567107525e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.573004995737051e-05</v>
+        <v>1.422584547143308e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.250023043396295e-05</v>
+        <v>1.230467072609557e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>2.104281561475526e-05</v>
+        <v>1.75172382587328e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.637888844878329e-05</v>
+        <v>1.456357844798738e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>3.399417266694602e-05</v>
+        <v>2.630659727470711e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.634174340014344e-05</v>
+        <v>1.470255796113687e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.857963376797499e-05</v>
+        <v>1.701256353918709e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>2.774582954277272e-05</v>
+        <v>2.126616020830695e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.802949796334861e-05</v>
+        <v>1.560160679067939e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.219739682622168e-05</v>
+        <v>1.926450393851615e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.820821196432935e-05</v>
+        <v>1.569649893260074e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.586781871414084e-05</v>
+        <v>1.9934171204127e-05</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.432185372026844e-05</v>
+        <v>1.968981049220918e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.264707572552218e-05</v>
+        <v>1.24385635753212e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.621680880850201e-05</v>
+        <v>1.459685915445794e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.450327169637474e-05</v>
+        <v>1.344547617192197e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.563549690807864e-05</v>
+        <v>1.423075236998143e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.512275314860227e-05</v>
+        <v>1.401520829811924e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.244266148201248e-05</v>
+        <v>1.235754672601824e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.791542004943603e-05</v>
+        <v>1.555621013893511e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.816333304255156e-05</v>
+        <v>1.583154948995236e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>2.128653128776633e-05</v>
+        <v>1.775190581906982e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>3.534636854563373e-05</v>
+        <v>2.623261646825345e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>2.117349785281528e-05</v>
+        <v>1.750532087471953e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.362360713820269e-05</v>
+        <v>1.305478542187222e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.731302506736113e-05</v>
+        <v>1.661264961824074e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>2.074411843685172e-05</v>
+        <v>1.750206700767678e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.699170476020249e-05</v>
+        <v>1.508390872682417e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.356098078576352e-05</v>
+        <v>1.300291596511869e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>2.064842739529269e-05</v>
+        <v>1.738252898325075e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.669858154756812e-05</v>
+        <v>1.483428764859762e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>3.662397900276796e-05</v>
+        <v>2.830144120774362e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.997336518245725e-05</v>
+        <v>1.705618015975446e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.990297749201586e-05</v>
+        <v>1.802816108639983e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>2.972707364122327e-05</v>
+        <v>2.263894228083697e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.200069071372606e-05</v>
+        <v>1.800605557395615e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.217517209700437e-05</v>
+        <v>1.947250431883887e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.884531015147703e-05</v>
+        <v>1.614978693835647e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.527470059797717e-05</v>
+        <v>1.972577401245756e-05</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.26934541983042e-05</v>
+        <v>1.204308054741916e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.118886801104111e-05</v>
+        <v>1.11360727522473e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.135724564983962e-05</v>
+        <v>1.121303375347627e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.136637026409172e-05</v>
+        <v>1.11542162682505e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.125168461425878e-05</v>
+        <v>1.114930820199087e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.214381876374814e-05</v>
+        <v>1.171045184796344e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.132848721863146e-05</v>
+        <v>1.119307412560327e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.141465075940322e-05</v>
+        <v>1.124576229642833e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.245888263160592e-05</v>
+        <v>1.189215551666849e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.196005730509683e-05</v>
+        <v>1.157638748264082e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>1.757794819554338e-05</v>
+        <v>1.509859427431411e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>1.43925060226112e-05</v>
+        <v>1.304303441829209e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.120312003581184e-05</v>
+        <v>1.112370682497325e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.315102367439834e-05</v>
+        <v>1.301096378173069e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.288222092164315e-05</v>
+        <v>1.215267719449076e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.152794031372332e-05</v>
+        <v>1.131717558871375e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.11672157348041e-05</v>
+        <v>1.110245649366505e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.213172457905733e-05</v>
+        <v>1.171207658546858e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.142706719613219e-05</v>
+        <v>1.125226569208272e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>2.076605594802558e-05</v>
+        <v>1.769339826812004e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.165763671728804e-05</v>
+        <v>1.140253434548275e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.506903882430949e-05</v>
+        <v>1.427398562070108e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.280455719047377e-05</v>
+        <v>1.206636771550858e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.147935892409949e-05</v>
+        <v>1.128816195020932e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.342640296080628e-05</v>
+        <v>1.28818457163377e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.372616549869633e-05</v>
+        <v>1.262370492555661e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.562021189207362e-05</v>
+        <v>1.368731472046518e-05</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.097607448658194e-05</v>
+        <v>1.090339963381057e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.105481961874682e-05</v>
+        <v>1.097929285100312e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.095135543904558e-05</v>
+        <v>1.08811085128153e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.08069375497167e-05</v>
+        <v>1.074871063615036e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.101315369346992e-05</v>
+        <v>1.092008162190475e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.119439538148714e-05</v>
+        <v>1.103263359326405e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.095655264430812e-05</v>
+        <v>1.088686362521255e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.114629807728429e-05</v>
+        <v>1.099871793322103e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.118932030492618e-05</v>
+        <v>1.102864457207291e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.142204351841554e-05</v>
+        <v>1.116674676366417e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>1.11691831407138e-05</v>
+        <v>1.101236811842719e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>1.122026741417063e-05</v>
+        <v>1.103873220113542e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.093907566928759e-05</v>
+        <v>1.087878690059344e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.252662558855301e-05</v>
+        <v>1.244541068626536e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.091243210348102e-05</v>
+        <v>1.086423201889042e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.095757072611036e-05</v>
+        <v>1.088584858760585e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.098800044531651e-05</v>
+        <v>1.090566847814319e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.13890017184997e-05</v>
+        <v>1.116036136488167e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.094986839172394e-05</v>
+        <v>1.087960846168208e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>1.294652630892636e-05</v>
+        <v>1.276848055346143e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.113731783468894e-05</v>
+        <v>1.099795221752986e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.337555524933514e-05</v>
+        <v>1.310967350299183e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.38604430648456e-05</v>
+        <v>1.263763913955364e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.227024753162558e-05</v>
+        <v>1.167068648528614e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.185492237050911e-05</v>
+        <v>1.173885521335454e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.143168324380874e-05</v>
+        <v>1.117339079208343e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.116988993701131e-05</v>
+        <v>1.101097966767494e-05</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.100230769087006e-05</v>
+        <v>1.091662516737496e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.105290880537572e-05</v>
+        <v>1.097676469135688e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.113741817327679e-05</v>
+        <v>1.09913745663007e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.075565379101906e-05</v>
+        <v>1.071130598688981e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.100006572989688e-05</v>
+        <v>1.091055033516381e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.102111463109369e-05</v>
+        <v>1.092379057473071e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.095002870525531e-05</v>
+        <v>1.08797325609845e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.119527978475041e-05</v>
+        <v>1.102532360609205e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.112258468934354e-05</v>
+        <v>1.098531298181246e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.167274503647411e-05</v>
+        <v>1.131469555545056e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>1.107857630962621e-05</v>
+        <v>1.095531619017404e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>1.120247251663649e-05</v>
+        <v>1.102737090518483e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.092495768177107e-05</v>
+        <v>1.086878390728392e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.251385781692315e-05</v>
+        <v>1.243320679067319e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.091803697822353e-05</v>
+        <v>1.086321910899192e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.098107432658599e-05</v>
+        <v>1.090013263697339e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.100225502680261e-05</v>
+        <v>1.091221128359947e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.126343494965679e-05</v>
+        <v>1.1076834438707e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.09860965398915e-05</v>
+        <v>1.090180297303334e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>1.299198815067602e-05</v>
+        <v>1.279081163727838e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.123950878532846e-05</v>
+        <v>1.106014394895762e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.295206759689388e-05</v>
+        <v>1.284100370171557e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.406439994390623e-05</v>
+        <v>1.276841604653311e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.187702264285432e-05</v>
+        <v>1.143276796421222e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.177345743066342e-05</v>
+        <v>1.168354178913543e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.115799249200503e-05</v>
+        <v>1.10082939519396e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.157883114259371e-05</v>
+        <v>1.124579881223113e-05</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.077112080582661e-05</v>
+        <v>1.723024669198634e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.180602177303275e-05</v>
+        <v>1.170087430745872e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.294570425697428e-05</v>
+        <v>1.237722040310866e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.468040412189328e-05</v>
+        <v>1.33442322584287e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.245725367469521e-05</v>
+        <v>1.209139969030462e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.436457667966968e-05</v>
+        <v>1.329303393239494e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.199052061948769e-05</v>
+        <v>1.181642643267076e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.226949409129557e-05</v>
+        <v>1.19820043172109e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.591709272229102e-05</v>
+        <v>1.420745650963549e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.212589896414367e-05</v>
+        <v>1.189868259237007e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>3.85810117053215e-05</v>
+        <v>2.78847635906105e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>2.169541631803392e-05</v>
+        <v>1.763700573527834e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.195347631081947e-05</v>
+        <v>1.180164699569749e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.507457000313987e-05</v>
+        <v>1.466889004624776e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.793146441041649e-05</v>
+        <v>1.54468855520848e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.315218705074317e-05</v>
+        <v>1.251302518170223e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.217289112761849e-05</v>
+        <v>1.192417729370008e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.625868908631349e-05</v>
+        <v>1.448315963274969e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.298673934759828e-05</v>
+        <v>1.24010594803945e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>3.035270522551411e-05</v>
+        <v>2.375781592006541e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.356490459388873e-05</v>
+        <v>1.280076397001194e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.667292777235755e-05</v>
+        <v>1.553369220029321e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>2.213223987493971e-05</v>
+        <v>1.777173114945722e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.44801233493843e-05</v>
+        <v>1.330886699069098e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.851232559941595e-05</v>
+        <v>1.650216174338294e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.631615251387783e-05</v>
+        <v>1.43942337981913e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.401200936765659e-05</v>
+        <v>1.870151484963335e-05</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.117145022319648e-05</v>
+        <v>1.110380771400057e-05</v>
       </c>
       <c r="C33" t="n">
-        <v>1.124439433800436e-05</v>
+        <v>1.117265141863377e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>1.157470507855569e-05</v>
+        <v>1.133805468084929e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.111335240453916e-05</v>
+        <v>1.100331647476044e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>1.117708288891947e-05</v>
+        <v>1.110238097395023e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.303767385190454e-05</v>
+        <v>1.22681250395352e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.114644399760501e-05</v>
+        <v>1.108683618836375e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>1.151228230918634e-05</v>
+        <v>1.130006411410147e-05</v>
       </c>
       <c r="J33" t="n">
-        <v>1.24808023880086e-05</v>
+        <v>1.190534687258033e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.263296191813091e-05</v>
+        <v>1.199200435151611e-05</v>
       </c>
       <c r="L33" t="n">
-        <v>1.910896665693371e-05</v>
+        <v>1.600630496379768e-05</v>
       </c>
       <c r="M33" t="n">
-        <v>1.261406091584306e-05</v>
+        <v>1.196471347320932e-05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.114176096306358e-05</v>
+        <v>1.108620490763082e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>1.309837354098324e-05</v>
+        <v>1.298365093133717e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>1.367366911681378e-05</v>
+        <v>1.264228312785705e-05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.118565247446987e-05</v>
+        <v>1.110738366113306e-05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.119255354404032e-05</v>
+        <v>1.111399760194185e-05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.221838214664167e-05</v>
+        <v>1.175336158300781e-05</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11668759049104e-05</v>
+        <v>1.109852158014358e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>1.539713833117058e-05</v>
+        <v>1.441243351967948e-05</v>
       </c>
       <c r="V33" t="n">
-        <v>1.138749533619106e-05</v>
+        <v>1.123210040649301e-05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.400511379191316e-05</v>
+        <v>1.362346146209559e-05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.75562543751308e-05</v>
+        <v>1.489610120004355e-05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.584666569438704e-05</v>
+        <v>1.388936736943862e-05</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.254790679605727e-05</v>
+        <v>1.22755305374909e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.277984050652656e-05</v>
+        <v>1.205811591139241e-05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.882244822152167e-05</v>
+        <v>1.552321754288882e-05</v>
       </c>
     </row>
   </sheetData>
